--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>136583125</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136583129</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79571</v>
+        <v>79575</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79571</v>
+        <v>79575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136583125</v>
       </c>
       <c r="B23" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136583129</v>
       </c>
       <c r="B24" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>136583128</v>
       </c>
       <c r="B62" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>136583127</v>
       </c>
       <c r="B67" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>136583126</v>
       </c>
       <c r="B106" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80370</v>
+        <v>80374</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79571</v>
+        <v>79575</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>136583130</v>
       </c>
       <c r="B165" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80370</v>
+        <v>80374</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79575</v>
+        <v>79577</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79575</v>
+        <v>79577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136583125</v>
       </c>
       <c r="B23" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136583129</v>
       </c>
       <c r="B24" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>136583128</v>
       </c>
       <c r="B62" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>136583127</v>
       </c>
       <c r="B67" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>136583126</v>
       </c>
       <c r="B106" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80374</v>
+        <v>80376</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79575</v>
+        <v>79577</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>136583130</v>
       </c>
       <c r="B165" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80374</v>
+        <v>80376</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79577</v>
+        <v>79578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79577</v>
+        <v>79578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136583125</v>
       </c>
       <c r="B23" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136583129</v>
       </c>
       <c r="B24" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>136583128</v>
       </c>
       <c r="B62" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>136583127</v>
       </c>
       <c r="B67" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>136583126</v>
       </c>
       <c r="B106" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80376</v>
+        <v>80377</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79577</v>
+        <v>79578</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>136583130</v>
       </c>
       <c r="B165" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80376</v>
+        <v>80377</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136583125</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136583129</v>
       </c>
       <c r="B24" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79578</v>
+        <v>79580</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79578</v>
+        <v>79580</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136583125</v>
       </c>
       <c r="B23" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136583129</v>
       </c>
       <c r="B24" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>136583128</v>
       </c>
       <c r="B62" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>136583127</v>
       </c>
       <c r="B67" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>136583126</v>
       </c>
       <c r="B106" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80377</v>
+        <v>80379</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79578</v>
+        <v>79580</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>136583130</v>
       </c>
       <c r="B165" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80377</v>
+        <v>80379</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -12196,7 +12196,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136583125</v>
       </c>
       <c r="B23" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>136583129</v>
       </c>
       <c r="B24" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>136583128</v>
       </c>
       <c r="B62" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>136583127</v>
       </c>
       <c r="B67" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>136583126</v>
       </c>
       <c r="B106" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80379</v>
+        <v>80382</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>136583130</v>
       </c>
       <c r="B165" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80379</v>
+        <v>80382</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79583</v>
+        <v>79596</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79583</v>
+        <v>79596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>136981985</v>
       </c>
       <c r="B99" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>136989014</v>
       </c>
       <c r="B100" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>136981857</v>
       </c>
       <c r="B101" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>136981863</v>
       </c>
       <c r="B102" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>136982016</v>
       </c>
       <c r="B103" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80382</v>
+        <v>80395</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79583</v>
+        <v>79596</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92052</v>
+        <v>92065</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92052</v>
+        <v>92065</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92052</v>
+        <v>92065</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92052</v>
+        <v>92065</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>136981938</v>
       </c>
       <c r="B174" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>136981972</v>
       </c>
       <c r="B175" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>136981926</v>
       </c>
       <c r="B176" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80382</v>
+        <v>80395</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79596</v>
+        <v>79598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79596</v>
+        <v>79598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>136981985</v>
       </c>
       <c r="B99" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>136989014</v>
       </c>
       <c r="B100" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>136981857</v>
       </c>
       <c r="B101" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>136981863</v>
       </c>
       <c r="B102" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>136982016</v>
       </c>
       <c r="B103" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80395</v>
+        <v>80397</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79596</v>
+        <v>79598</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>136981938</v>
       </c>
       <c r="B174" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>136981972</v>
       </c>
       <c r="B175" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>136981926</v>
       </c>
       <c r="B176" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80395</v>
+        <v>80397</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -11620,11 +11620,7 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vålåberget norra, Dlr</t>
@@ -11741,11 +11737,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Vålåberget N, Dlr</t>
@@ -11974,16 +11966,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vålåberget norra, Dlr</t>
@@ -12100,16 +12084,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vålåberget norra, Dlr</t>
@@ -20296,11 +20272,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Vålåberget norra, Dlr</t>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92067</v>
+        <v>92070</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92067</v>
+        <v>92070</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92067</v>
+        <v>92070</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92067</v>
+        <v>92070</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79598</v>
+        <v>79608</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>79608</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>136981985</v>
       </c>
       <c r="B99" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>136989014</v>
       </c>
       <c r="B100" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>136981857</v>
       </c>
       <c r="B101" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>136981863</v>
       </c>
       <c r="B102" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>136982016</v>
       </c>
       <c r="B103" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80397</v>
+        <v>80407</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79598</v>
+        <v>79608</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92070</v>
+        <v>92080</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92070</v>
+        <v>92080</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92070</v>
+        <v>92080</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92070</v>
+        <v>92080</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>136981938</v>
       </c>
       <c r="B174" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>136981972</v>
       </c>
       <c r="B175" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>136981926</v>
       </c>
       <c r="B176" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80397</v>
+        <v>80407</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
+        <v>79611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79608</v>
+        <v>79611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>136981985</v>
       </c>
       <c r="B99" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>136989014</v>
       </c>
       <c r="B100" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>136981857</v>
       </c>
       <c r="B101" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>136981863</v>
       </c>
       <c r="B102" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>136982016</v>
       </c>
       <c r="B103" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79608</v>
+        <v>79611</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93481</v>
+        <v>93486</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92081</v>
+        <v>92084</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92081</v>
+        <v>92084</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92081</v>
+        <v>92084</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92081</v>
+        <v>92084</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>136981938</v>
       </c>
       <c r="B174" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>136981972</v>
       </c>
       <c r="B175" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>136981926</v>
       </c>
       <c r="B176" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93486</v>
+        <v>93488</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92084</v>
+        <v>92086</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92084</v>
+        <v>92086</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92084</v>
+        <v>92086</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92084</v>
+        <v>92086</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79611</v>
+        <v>79616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79611</v>
+        <v>79616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90756</v>
+        <v>90761</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>136981985</v>
       </c>
       <c r="B99" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>136981857</v>
       </c>
       <c r="B101" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>136981863</v>
       </c>
       <c r="B102" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>136982016</v>
       </c>
       <c r="B103" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79611</v>
+        <v>79616</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93488</v>
+        <v>93494</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92086</v>
+        <v>92091</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92086</v>
+        <v>92091</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92086</v>
+        <v>92091</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92086</v>
+        <v>92091</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>136981938</v>
       </c>
       <c r="B174" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>136981972</v>
       </c>
       <c r="B175" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>136981926</v>
       </c>
       <c r="B176" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79616</v>
+        <v>79627</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79616</v>
+        <v>79627</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80415</v>
+        <v>80426</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79616</v>
+        <v>79627</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93494</v>
+        <v>93506</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92091</v>
+        <v>92103</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92091</v>
+        <v>92103</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92091</v>
+        <v>92103</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92091</v>
+        <v>92103</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80415</v>
+        <v>80426</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79627</v>
+        <v>79628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79627</v>
+        <v>79628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93512</v>
+        <v>93513</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93512</v>
+        <v>93513</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80426</v>
+        <v>80427</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79627</v>
+        <v>79628</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93506</v>
+        <v>93507</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92103</v>
+        <v>92104</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92103</v>
+        <v>92104</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92103</v>
+        <v>92104</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92103</v>
+        <v>92104</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80426</v>
+        <v>80427</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79628</v>
+        <v>79630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79628</v>
+        <v>79630</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104158</v>
+        <v>104161</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104158</v>
+        <v>104161</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93513</v>
+        <v>93516</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93513</v>
+        <v>93516</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80427</v>
+        <v>80429</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79628</v>
+        <v>79630</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93507</v>
+        <v>93510</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92104</v>
+        <v>92107</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92104</v>
+        <v>92107</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92104</v>
+        <v>92107</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92104</v>
+        <v>92107</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80427</v>
+        <v>80429</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79630</v>
+        <v>79631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79630</v>
+        <v>79631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90776</v>
+        <v>90777</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93511</v>
+        <v>93512</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80662</v>
+        <v>80663</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78535</v>
+        <v>78536</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104161</v>
+        <v>104162</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104161</v>
+        <v>104162</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93516</v>
+        <v>93517</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93516</v>
+        <v>93517</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80429</v>
+        <v>80430</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79630</v>
+        <v>79631</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93510</v>
+        <v>93511</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92107</v>
+        <v>92108</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92107</v>
+        <v>92108</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92107</v>
+        <v>92108</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92107</v>
+        <v>92108</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93511</v>
+        <v>93512</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93511</v>
+        <v>93512</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80429</v>
+        <v>80430</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 39058-2026 artfynd.xlsx
+++ b/artfynd/A 39058-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136981847</v>
       </c>
       <c r="B2" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136981856</v>
       </c>
       <c r="B3" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136981867</v>
       </c>
       <c r="B4" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136981872</v>
       </c>
       <c r="B5" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136981873</v>
       </c>
       <c r="B6" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136981875</v>
       </c>
       <c r="B7" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136981990</v>
       </c>
       <c r="B8" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136981999</v>
       </c>
       <c r="B9" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136982001</v>
       </c>
       <c r="B10" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136982013</v>
       </c>
       <c r="B11" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136981897</v>
       </c>
       <c r="B12" t="n">
-        <v>79631</v>
+        <v>79634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>136981989</v>
       </c>
       <c r="B13" t="n">
-        <v>79631</v>
+        <v>79634</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136981864</v>
       </c>
       <c r="B14" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>136981879</v>
       </c>
       <c r="B15" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136981919</v>
       </c>
       <c r="B16" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136981995</v>
       </c>
       <c r="B17" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136981866</v>
       </c>
       <c r="B18" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136981851</v>
       </c>
       <c r="B25" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>136981852</v>
       </c>
       <c r="B26" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136981853</v>
       </c>
       <c r="B27" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>136981855</v>
       </c>
       <c r="B28" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>136981860</v>
       </c>
       <c r="B29" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136981876</v>
       </c>
       <c r="B30" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136981877</v>
       </c>
       <c r="B31" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>136981878</v>
       </c>
       <c r="B32" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136981883</v>
       </c>
       <c r="B33" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>136981884</v>
       </c>
       <c r="B34" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>136981907</v>
       </c>
       <c r="B35" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136981908</v>
       </c>
       <c r="B36" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136981913</v>
       </c>
       <c r="B37" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136981914</v>
       </c>
       <c r="B38" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>136981923</v>
       </c>
       <c r="B39" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>136981979</v>
       </c>
       <c r="B40" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>136981981</v>
       </c>
       <c r="B41" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136981982</v>
       </c>
       <c r="B42" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>136981983</v>
       </c>
       <c r="B43" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>136981987</v>
       </c>
       <c r="B44" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136981988</v>
       </c>
       <c r="B45" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>136981993</v>
       </c>
       <c r="B46" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>136981998</v>
       </c>
       <c r="B47" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>136982000</v>
       </c>
       <c r="B48" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>136982009</v>
       </c>
       <c r="B49" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>136982010</v>
       </c>
       <c r="B50" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>136982011</v>
       </c>
       <c r="B51" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>136982022</v>
       </c>
       <c r="B52" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>136989019</v>
       </c>
       <c r="B53" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>136989024</v>
       </c>
       <c r="B54" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>136989025</v>
       </c>
       <c r="B55" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>136989031</v>
       </c>
       <c r="B56" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>136982021</v>
       </c>
       <c r="B57" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>136981997</v>
       </c>
       <c r="B58" t="n">
-        <v>90777</v>
+        <v>90780</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>136981980</v>
       </c>
       <c r="B59" t="n">
-        <v>93512</v>
+        <v>93515</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>136981862</v>
       </c>
       <c r="B60" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>136989030</v>
       </c>
       <c r="B61" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136981881</v>
       </c>
       <c r="B63" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>136981896</v>
       </c>
       <c r="B64" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136981903</v>
       </c>
       <c r="B65" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136982006</v>
       </c>
       <c r="B66" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>136981849</v>
       </c>
       <c r="B68" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>136981870</v>
       </c>
       <c r="B69" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136981905</v>
       </c>
       <c r="B70" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>136981918</v>
       </c>
       <c r="B71" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>136981978</v>
       </c>
       <c r="B72" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>136981994</v>
       </c>
       <c r="B73" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>136982005</v>
       </c>
       <c r="B74" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>136982019</v>
       </c>
       <c r="B75" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>136989026</v>
       </c>
       <c r="B76" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>136989033</v>
       </c>
       <c r="B77" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>136981869</v>
       </c>
       <c r="B78" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>136981874</v>
       </c>
       <c r="B79" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>136981882</v>
       </c>
       <c r="B80" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>136981885</v>
       </c>
       <c r="B81" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>136981886</v>
       </c>
       <c r="B82" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>136981888</v>
       </c>
       <c r="B83" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>136981893</v>
       </c>
       <c r="B84" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>136981916</v>
       </c>
       <c r="B85" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>136981976</v>
       </c>
       <c r="B86" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>136981992</v>
       </c>
       <c r="B87" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>136982002</v>
       </c>
       <c r="B88" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>136982007</v>
       </c>
       <c r="B89" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>136982008</v>
       </c>
       <c r="B90" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>136982020</v>
       </c>
       <c r="B91" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136982023</v>
       </c>
       <c r="B92" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>136989018</v>
       </c>
       <c r="B93" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>136989020</v>
       </c>
       <c r="B94" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>136989021</v>
       </c>
       <c r="B95" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>136989028</v>
       </c>
       <c r="B96" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136989015</v>
       </c>
       <c r="B97" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>136981901</v>
       </c>
       <c r="B98" t="n">
-        <v>78536</v>
+        <v>78539</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>136981985</v>
       </c>
       <c r="B99" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>136989014</v>
       </c>
       <c r="B100" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>136981857</v>
       </c>
       <c r="B101" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>136981863</v>
       </c>
       <c r="B102" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>136982016</v>
       </c>
       <c r="B103" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>136989016</v>
       </c>
       <c r="B104" t="n">
-        <v>104162</v>
+        <v>104166</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>136989017</v>
       </c>
       <c r="B105" t="n">
-        <v>104162</v>
+        <v>104166</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>136981848</v>
       </c>
       <c r="B107" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>136981859</v>
       </c>
       <c r="B108" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>136981887</v>
       </c>
       <c r="B109" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136981895</v>
       </c>
       <c r="B110" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>136981922</v>
       </c>
       <c r="B111" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>136981977</v>
       </c>
       <c r="B112" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>136982004</v>
       </c>
       <c r="B113" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>136982018</v>
       </c>
       <c r="B114" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>136989027</v>
       </c>
       <c r="B115" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>136981861</v>
       </c>
       <c r="B116" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>136981880</v>
       </c>
       <c r="B117" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>136981889</v>
       </c>
       <c r="B118" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>136981894</v>
       </c>
       <c r="B119" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136981898</v>
       </c>
       <c r="B120" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136981921</v>
       </c>
       <c r="B121" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136981984</v>
       </c>
       <c r="B122" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136982015</v>
       </c>
       <c r="B123" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>136989029</v>
       </c>
       <c r="B124" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>136981858</v>
       </c>
       <c r="B125" t="n">
-        <v>93517</v>
+        <v>93520</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>136981915</v>
       </c>
       <c r="B126" t="n">
-        <v>93517</v>
+        <v>93520</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>136981902</v>
       </c>
       <c r="B127" t="n">
-        <v>80430</v>
+        <v>80433</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>136981933</v>
       </c>
       <c r="B128" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>136981942</v>
       </c>
       <c r="B129" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>136981951</v>
       </c>
       <c r="B130" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136981966</v>
       </c>
       <c r="B131" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>136981975</v>
       </c>
       <c r="B132" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>136981948</v>
       </c>
       <c r="B133" t="n">
-        <v>79631</v>
+        <v>79634</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>136981911</v>
       </c>
       <c r="B134" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>136981928</v>
       </c>
       <c r="B135" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>136981939</v>
       </c>
       <c r="B136" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>136981968</v>
       </c>
       <c r="B137" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>136981955</v>
       </c>
       <c r="B138" t="n">
-        <v>93511</v>
+        <v>93514</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>136981910</v>
       </c>
       <c r="B139" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>136981924</v>
       </c>
       <c r="B140" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>136981973</v>
       </c>
       <c r="B141" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>136981974</v>
       </c>
       <c r="B142" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>136981890</v>
       </c>
       <c r="B144" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>136981892</v>
       </c>
       <c r="B145" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>136981909</v>
       </c>
       <c r="B146" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>136981927</v>
       </c>
       <c r="B147" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136981929</v>
       </c>
       <c r="B148" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>136981944</v>
       </c>
       <c r="B149" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>136981950</v>
       </c>
       <c r="B150" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>136981953</v>
       </c>
       <c r="B151" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>136981954</v>
       </c>
       <c r="B152" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>136981958</v>
       </c>
       <c r="B153" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>136981960</v>
       </c>
       <c r="B154" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>136981962</v>
       </c>
       <c r="B155" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>136981925</v>
       </c>
       <c r="B157" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>136981965</v>
       </c>
       <c r="B158" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>136981936</v>
       </c>
       <c r="B159" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>136981945</v>
       </c>
       <c r="B160" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>136981946</v>
       </c>
       <c r="B161" t="n">
-        <v>93512</v>
+        <v>93515</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>136981964</v>
       </c>
       <c r="B162" t="n">
-        <v>93512</v>
+        <v>93515</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>136981949</v>
       </c>
       <c r="B163" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>136981943</v>
       </c>
       <c r="B164" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>136981900</v>
       </c>
       <c r="B166" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>136981959</v>
       </c>
       <c r="B167" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>136981971</v>
       </c>
       <c r="B168" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>136981920</v>
       </c>
       <c r="B169" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>136981937</v>
       </c>
       <c r="B170" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136981952</v>
       </c>
       <c r="B171" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>136981963</v>
       </c>
       <c r="B172" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>136981969</v>
       </c>
       <c r="B173" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>136981938</v>
       </c>
       <c r="B174" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>136981972</v>
       </c>
       <c r="B175" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>136981926</v>
       </c>
       <c r="B176" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136981930</v>
       </c>
       <c r="B177" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>136981912</v>
       </c>
       <c r="B178" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>136981940</v>
       </c>
       <c r="B179" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>136981947</v>
       </c>
       <c r="B180" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>136981941</v>
       </c>
       <c r="B181" t="n">
-        <v>80430</v>
+        <v>80433</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
